--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80556</v>
+        <v>80558</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80561</v>
+        <v>80563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80558</v>
+        <v>80559</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80563</v>
+        <v>80564</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80559</v>
+        <v>80560</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80560</v>
+        <v>80564</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80564</v>
+        <v>80565</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80569</v>
+        <v>80570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80565</v>
+        <v>80569</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80570</v>
+        <v>80574</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80569</v>
+        <v>80575</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80574</v>
+        <v>80580</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80575</v>
+        <v>80588</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80580</v>
+        <v>80593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 62526-2025 artfynd.xlsx
+++ b/artfynd/A 62526-2025 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135912276</v>
       </c>
       <c r="B2" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135912342</v>
       </c>
       <c r="B3" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -887,7 +887,7 @@
         <v>135912378</v>
       </c>
       <c r="B4" t="n">
-        <v>80588</v>
+        <v>80589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -989,7 +989,7 @@
         <v>135912348</v>
       </c>
       <c r="B5" t="n">
-        <v>80593</v>
+        <v>80594</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
